--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>43482850</v>
       </c>
       <c r="B22" t="n">
-        <v>57203</v>
+        <v>57204</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>49680576</v>
       </c>
       <c r="B24" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3545,6 +3545,125 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123403975</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57398</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S25" t="n">
+        <v>62</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>satt i ett träd precis vid E45:an</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Peter Bäck</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Peter Bäck</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -3550,7 +3550,7 @@
         <v>123403975</v>
       </c>
       <c r="B25" t="n">
-        <v>57398</v>
+        <v>57401</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3550,7 +3550,7 @@
         <v>123403975</v>
       </c>
       <c r="B25" t="n">
-        <v>57401</v>
+        <v>57407</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3663,6 +3663,132 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>46444123</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57484</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S26" t="n">
+        <v>62</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-06-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -3550,7 +3550,7 @@
         <v>123403975</v>
       </c>
       <c r="B25" t="n">
-        <v>57407</v>
+        <v>57410</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3666,10 +3666,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46444123</v>
+        <v>45744376</v>
       </c>
       <c r="B26" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3701,17 +3701,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3750,7 +3745,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2013-05-06</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3760,12 +3755,17 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2013-06-18</t>
+          <t>2013-05-06</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Undersöker en holk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -3550,7 +3550,7 @@
         <v>123403975</v>
       </c>
       <c r="B25" t="n">
-        <v>57410</v>
+        <v>57411</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3666,14 +3666,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45744376</v>
+        <v>29422065</v>
       </c>
       <c r="B26" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3701,12 +3701,22 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3745,7 +3755,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2013-05-06</t>
+          <t>2008-06-14</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3755,17 +3765,12 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2013-05-06</t>
+          <t>2008-06-14</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Undersöker en holk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3785,7 +3790,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -4018,7 +4018,7 @@
         <v>132024561</v>
       </c>
       <c r="B29" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -2658,12 +2658,7 @@
         <v>23189683</v>
       </c>
       <c r="B18" t="n">
-        <v>56999</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,10 +2709,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R18" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S18" t="n">
         <v>62</v>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -2658,7 +2658,7 @@
         <v>23189683</v>
       </c>
       <c r="B18" t="n">
-        <v>58581</v>
+        <v>58582</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>132024561</v>
       </c>
       <c r="B29" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -2658,7 +2658,7 @@
         <v>23189683</v>
       </c>
       <c r="B18" t="n">
-        <v>58582</v>
+        <v>58586</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>132024561</v>
       </c>
       <c r="B29" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -2658,7 +2658,7 @@
         <v>23189683</v>
       </c>
       <c r="B18" t="n">
-        <v>58586</v>
+        <v>58587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4126,6 +4126,120 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134154922</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57959</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S30" t="n">
+        <v>62</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Satt i toppen av torrakan på hygget.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -4131,7 +4131,7 @@
         <v>134154922</v>
       </c>
       <c r="B30" t="n">
-        <v>57959</v>
+        <v>57969</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4240,6 +4240,138 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134327920</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S31" t="n">
+        <v>62</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hördes från bergåsen vid Nybyggerud. Bra spel.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17389-2024 artfynd.xlsx
+++ b/artfynd/A 17389-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19369655</v>
+        <v>21342300</v>
       </c>
       <c r="B2" t="n">
-        <v>56539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +708,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R2" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S2" t="n">
         <v>62</v>
@@ -749,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2005-09-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2005-09-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>AMNEBYN 1:18</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,42 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>19382751</v>
+        <v>31720130</v>
       </c>
       <c r="B3" t="n">
-        <v>57063</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R3" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S3" t="n">
         <v>62</v>
@@ -870,27 +865,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2009-03-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2009-03-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>AMNEBYN 1:18</t>
+          <t>Från betesfälten mot Vänern.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19266367</v>
+        <v>19373945</v>
       </c>
       <c r="B4" t="n">
-        <v>56537</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,16 +923,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,9 +945,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R4" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S4" t="n">
         <v>62</v>
@@ -996,7 +991,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1006,7 +1001,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-02-10</t>
+          <t>2003-05-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1016,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Amnebyn 1:18</t>
+          <t>NYBYGGERUD/TRUMNING/LÄTE</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,37 +1038,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19308969</v>
+        <v>20455652</v>
       </c>
       <c r="B5" t="n">
-        <v>55915</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102957</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartsnäppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tringa erythropus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,7 +1073,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1092,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R5" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S5" t="n">
         <v>62</v>
@@ -1122,7 +1112,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1132,7 +1122,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2003-06-21</t>
+          <t>2002-01-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1142,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>LOCKLÄTE</t>
+          <t>Endast hörd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,37 +1159,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>19399540</v>
+        <v>20986532</v>
       </c>
       <c r="B6" t="n">
-        <v>55833</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100091</v>
+        <v>100063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Smålom</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Gavia stellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1207,16 +1192,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R6" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S6" t="n">
         <v>62</v>
@@ -1243,27 +1238,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2004-04-21</t>
+          <t>2005-05-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2004-04-21</t>
+          <t>2005-05-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Överflygande, lockläte.</t>
+          <t>Endast hörd. "Kacklande".</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,32 +1285,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19710881</v>
+        <v>19463760</v>
       </c>
       <c r="B7" t="n">
-        <v>56607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102981</v>
+        <v>100065</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,12 +1315,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>sträckande O</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1339,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R7" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S7" t="n">
         <v>62</v>
@@ -1369,22 +1359,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2004-03-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2004-05-05</t>
+          <t>2004-03-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,37 +1401,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19703687</v>
+        <v>43482850</v>
       </c>
       <c r="B8" t="n">
-        <v>56858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1449,14 +1434,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1K</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1465,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R8" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S8" t="n">
         <v>62</v>
@@ -1495,22 +1480,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2012-08-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2004-05-02</t>
+          <t>2012-08-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>AL, fick se den rakt över huset !</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,22 +1520,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>19867297</v>
+        <v>19399540</v>
       </c>
       <c r="B9" t="n">
-        <v>55666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,16 +1538,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102976</v>
+        <v>100091</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1575,21 +1560,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>sträckande S</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R9" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S9" t="n">
         <v>62</v>
@@ -1616,22 +1596,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2004-04-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2004-08-21</t>
+          <t>2004-04-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Överflygande, lockläte.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,32 +1643,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20455652</v>
+        <v>40529156</v>
       </c>
       <c r="B10" t="n">
-        <v>56410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100096</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1698,7 +1678,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1707,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R10" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S10" t="n">
         <v>62</v>
@@ -1737,27 +1717,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2002-01-09</t>
+          <t>2011-07-27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Endast hörd.</t>
+          <t>På hög höjd över huset. Upptäcktes gm. locklätet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,69 +1764,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20570227</v>
+        <v>123403975</v>
       </c>
       <c r="B11" t="n">
-        <v>57006</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103042</v>
+        <v>102110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>rastande</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R11" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S11" t="n">
         <v>62</v>
@@ -1873,22 +1841,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2002-02-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>satt i ett träd precis vid E45:an</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1903,49 +1866,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Peter Bäck</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Peter Bäck</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21091630</v>
+        <v>134327920</v>
       </c>
       <c r="B12" t="n">
-        <v>56716</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103008</v>
+        <v>102118</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1953,21 +1911,32 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R12" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S12" t="n">
         <v>62</v>
@@ -1994,22 +1963,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2005-05-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hördes från bergåsen vid Nybyggerud. Bra spel.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2036,15 +2010,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>21040568</v>
+        <v>19716929</v>
       </c>
       <c r="B13" t="n">
-        <v>56805</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,21 +2021,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>102119</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2085,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R13" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S13" t="n">
         <v>62</v>
@@ -2115,7 +2084,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2125,12 +2094,17 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2005-04-14</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vid holk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,15 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20986532</v>
+        <v>18955902</v>
       </c>
       <c r="B14" t="n">
-        <v>56098</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2173,21 +2142,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100063</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smålom</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gavia stellata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2195,14 +2164,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sträckande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2211,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R14" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S14" t="n">
         <v>62</v>
@@ -2241,27 +2205,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2005-05-28</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2005-05-28</t>
+          <t>2004-01-27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Endast hörd. "Kacklande".</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2288,47 +2252,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21582210</v>
+        <v>36639635</v>
       </c>
       <c r="B15" t="n">
-        <v>56400</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>102626</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2337,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R15" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S15" t="n">
         <v>62</v>
@@ -2367,7 +2336,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2377,12 +2346,17 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2004-08-15</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På hygget.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,27 +2371,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dalslands rapportkommitté</t>
+          <t>Erik Höök</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Erik Höök, Björn Höök</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21342300</v>
+        <v>19308969</v>
       </c>
       <c r="B16" t="n">
-        <v>56285</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,21 +2394,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>102957</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Svartsnäppa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tringa erythropus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2449,7 +2418,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2458,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R16" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S16" t="n">
         <v>62</v>
@@ -2488,22 +2457,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2005-09-13</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2005-09-13</t>
+          <t>2003-06-21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>LOCKLÄTE</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2530,15 +2504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>21738225</v>
+        <v>32164526</v>
       </c>
       <c r="B17" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2546,21 +2515,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103035</v>
+        <v>102963</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2570,7 +2539,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2579,10 +2548,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R17" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S17" t="n">
         <v>62</v>
@@ -2609,22 +2578,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2005-10-02</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2005-10-02</t>
+          <t>2009-04-30</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2647,60 +2616,51 @@
           <t>Björn Höök</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>EuroBirdwatch</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23189683</v>
+        <v>24309323</v>
       </c>
       <c r="B18" t="n">
-        <v>58591</v>
+        <v>57802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103051</v>
+        <v>102975</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Hornuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Asio otus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2K</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>pulli</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2739,27 +2699,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2006-07-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2006-05-19</t>
+          <t>2006-07-17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,32 +2741,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24309323</v>
+        <v>19867297</v>
       </c>
       <c r="B19" t="n">
-        <v>56354</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102975</v>
+        <v>102976</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hornuggla</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asio otus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2821,17 +2771,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>pulli</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2840,10 +2785,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R19" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S19" t="n">
         <v>62</v>
@@ -2870,22 +2815,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2006-07-02</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2006-07-17</t>
+          <t>2004-08-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2912,32 +2857,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>28993536</v>
+        <v>20449044</v>
       </c>
       <c r="B20" t="n">
-        <v>56778</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103037</v>
+        <v>102977</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2952,7 +2892,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2961,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R20" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S20" t="n">
         <v>62</v>
@@ -2991,27 +2931,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2008-04-04</t>
+          <t>2002-01-08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål i asp.</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3038,15 +2973,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>32164526</v>
+        <v>23361936</v>
       </c>
       <c r="B21" t="n">
-        <v>55945</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3054,31 +2984,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102963</v>
+        <v>102980</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3087,10 +3017,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R21" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S21" t="n">
         <v>62</v>
@@ -3117,7 +3047,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3127,7 +3057,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2009-04-30</t>
+          <t>2006-05-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3159,32 +3089,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>43482850</v>
+        <v>19710881</v>
       </c>
       <c r="B22" t="n">
-        <v>57206</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100067</v>
+        <v>102981</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3194,17 +3119,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3243,27 +3163,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2012-08-19</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2012-08-19</t>
+          <t>2004-05-05</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>AL, fick se den rakt över huset !</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3283,22 +3198,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45636766</v>
+        <v>26759486</v>
       </c>
       <c r="B23" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3306,16 +3216,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102964</v>
+        <v>102987</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3325,12 +3235,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3339,10 +3254,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>364641.6501244664</v>
+        <v>364642</v>
       </c>
       <c r="R23" t="n">
-        <v>6540380.526146653</v>
+        <v>6540381</v>
       </c>
       <c r="S23" t="n">
         <v>62</v>
@@ -3369,7 +3284,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2013-04-20</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3379,7 +3294,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2013-04-20</t>
+          <t>2007-05-25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3389,7 +3304,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Överflygande</t>
+          <t>Holkhäckning i starholk!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3416,15 +3331,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>49680576</v>
+        <v>19764908</v>
       </c>
       <c r="B24" t="n">
-        <v>57537</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3432,21 +3342,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3495,27 +3405,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-05-20</t>
+          <t>2004-04-16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Även lockläte. Tomtkryss!</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3535,22 +3440,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123403975</v>
+        <v>21040568</v>
       </c>
       <c r="B25" t="n">
-        <v>57433</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3558,21 +3458,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102110</v>
+        <v>103001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3580,14 +3480,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -3624,17 +3521,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2005-04-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>satt i ett träd precis vid E45:an</t>
+          <t>2005-04-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3649,27 +3551,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Peter Bäck</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Peter Bäck</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46345406</v>
+        <v>21091630</v>
       </c>
       <c r="B26" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58286</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3677,21 +3574,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102119</v>
+        <v>103008</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3701,7 +3598,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3740,7 +3637,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3750,7 +3647,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2005-05-17</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3775,50 +3672,51 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Björn Höök, Anna-lena Höök</t>
+          <t>Björn Höök</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131652091</v>
+        <v>49680576</v>
       </c>
       <c r="B27" t="n">
-        <v>57253</v>
+        <v>58238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100065</v>
+        <v>103012</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -3855,17 +3753,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2014-05-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2014-05-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I närområdet, ljudliga.</t>
+          <t>Även lockläte. Tomtkryss!</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3885,17 +3793,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Björn Höök</t>
+          <t>Björn Höök, Anna-lena Höök</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131714999</v>
+        <v>20180506</v>
       </c>
       <c r="B28" t="n">
-        <v>56920</v>
+        <v>58327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3903,16 +3811,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100045</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3930,13 +3838,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -3973,17 +3879,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2005-01-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Lågt över huset, V-ut.</t>
+          <t>2005-01-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4010,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132024561</v>
+        <v>19703687</v>
       </c>
       <c r="B29" t="n">
-        <v>58497</v>
+        <v>58439</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4021,21 +3932,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102990</v>
+        <v>103018</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4043,18 +3954,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4091,17 +4000,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Matningen.</t>
+          <t>2004-05-02</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4128,10 +4042,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134154922</v>
+        <v>131566195</v>
       </c>
       <c r="B30" t="n">
-        <v>57969</v>
+        <v>58250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4139,21 +4053,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102977</v>
+        <v>103019</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4161,11 +4075,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4205,17 +4123,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Satt i toppen av torrakan på hygget.</t>
+          <t>Matningen. Verkar som familjegrupperna har skingrats. Kanske ett häckningspar i närområdet.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4242,32 +4160,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134327920</v>
+        <v>19266367</v>
       </c>
       <c r="B31" t="n">
-        <v>57776</v>
+        <v>58112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102118</v>
+        <v>103020</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4275,22 +4193,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Furulyckan, Amnebyn, Tösse, Dls</t>
@@ -4327,27 +4234,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>02:11</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2004-02-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hördes från bergåsen vid Nybyggerud. Bra spel.</t>
+          <t>Amnebyn 1:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4371,6 +4278,983 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>19369655</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S32" t="n">
+        <v>62</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>AMNEBYN 1:18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131566149</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S33" t="n">
+        <v>62</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Matningen.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132787274</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58104</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S34" t="n">
+        <v>62</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Matningen.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>28993536</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S35" t="n">
+        <v>62</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2008-04-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bohål i asp.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20570227</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S36" t="n">
+        <v>62</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2002-02-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2002-02-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20559366</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S37" t="n">
+        <v>62</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2002-02-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2002-02-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Vinterdräkt.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>23189683</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58608</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S38" t="n">
+        <v>62</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2006-05-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2006-05-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fågelmatningen tillsammans med bofink och grönfink.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>19382751</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Furulyckan, Amnebyn, Tösse, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>364642</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6540381</v>
+      </c>
+      <c r="S39" t="n">
+        <v>62</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tösse</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>AMNEBYN 1:18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Björn Höök</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
